--- a/public/exports-from-60/29189757.xlsx
+++ b/public/exports-from-60/29189757.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054922</t>
+          <t xml:space="preserve">200054923</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">

--- a/public/exports-from-60/29189757.xlsx
+++ b/public/exports-from-60/29189757.xlsx
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054923</t>
+          <t xml:space="preserve">200054922</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">

--- a/public/exports-from-60/29189757.xlsx
+++ b/public/exports-from-60/29189757.xlsx
@@ -15664,7 +15664,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
